--- a/data/usa/p6_deployment/data_understanding/df_match_next_odds.xlsx
+++ b/data/usa/p6_deployment/data_understanding/df_match_next_odds.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,310 +448,330 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>AszX60rp</t>
+          <t>hQiNHHd2</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>4.20</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>2.88</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>jix3jCxF</t>
+          <t>C6QBlj7R</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>2.60</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>h6Py6Kcj</t>
+          <t>dbI3Q902</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>2.75</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>WdOu5vDd</t>
+          <t>zkH7PTF8</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>3.20</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>KCHNTNkc</t>
+          <t>UPVAOmVE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>3.90</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>2.55</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>b3GRSs53</t>
+          <t>8GUEN7pL</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t>4.10</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
           <t>3.90</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>3.50</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>tS5WR1K9</t>
+          <t>juKJMRaR</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>4.20</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>2.25</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>h29zRLZF</t>
+          <t>Usy7kWiL</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>2.40</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>QF7rPa4S</t>
+          <t>lSHwpAFr</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>3.20</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>nP8vQukM</t>
+          <t>MNAkH5Nl</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>3.90</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>2.60</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>69kBKJCq</t>
+          <t>S0BoIo8r</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>2.40</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>vNmJIcsd</t>
+          <t>0E9gGPxe</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>4.75</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>MHXbihN8</t>
+          <t>Ik4bFqh1</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>4.20</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>p0lFJwSk</t>
+          <t>dt32E377</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>3.20</t>
-        </is>
-      </c>
+          <t>3.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>vqenBDBt</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>SWX9C8ZI</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/usa/p6_deployment/data_understanding/df_match_next_odds.xlsx
+++ b/data/usa/p6_deployment/data_understanding/df_match_next_odds.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,73 +448,73 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hQiNHHd2</t>
+          <t>hIoLKAg0</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>4.10</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>C6QBlj7R</t>
+          <t>KEflYcbt</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>3.20</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>dbI3Q902</t>
+          <t>EyfhXHDn</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>4.10</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>5.00</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>zkH7PTF8</t>
+          <t>SvbdWyTh</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -524,254 +524,58 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>3.60</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>UPVAOmVE</t>
+          <t>AoWGqXpJ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>3.10</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>8GUEN7pL</t>
+          <t>trWntSE7</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>4.10</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>3.90</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>juKJMRaR</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2.50</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>3.75</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>Usy7kWiL</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2.40</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>2.40</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>lSHwpAFr</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>1.95</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>MNAkH5Nl</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>2.60</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>S0BoIo8r</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2.40</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>2.40</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>0E9gGPxe</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>1.53</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>4.75</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>Ik4bFqh1</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>1.60</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>4.20</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>dt32E377</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>1.80</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
           <t>3.80</t>
         </is>
       </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>vqenBDBt</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>SWX9C8ZI</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/usa/p6_deployment/data_understanding/df_match_next_odds.xlsx
+++ b/data/usa/p6_deployment/data_understanding/df_match_next_odds.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -485,7 +485,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>3.10</t>
         </is>
       </c>
     </row>
@@ -524,7 +524,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -541,17 +541,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>3.40</t>
         </is>
       </c>
     </row>
@@ -563,17 +563,303 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>A3m1Vera</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>8lOY3V6E</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>ITj9TZCB</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>lfn5UFc5</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>dKkDSgSH</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>vquIRDsO</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>1.66</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>jDDw3kMK</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
           <t>3.50</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>xUcLQXdU</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>EkZQoHSu</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
         <is>
           <t>3.80</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>htYUpyrn</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>AHSZqech</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>l8RwqFCb</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>foKU4Bi8</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>4.60</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>6.50</t>
         </is>
       </c>
     </row>

--- a/data/usa/p6_deployment/data_understanding/df_match_next_odds.xlsx
+++ b/data/usa/p6_deployment/data_understanding/df_match_next_odds.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,34 +448,34 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hIoLKAg0</t>
+          <t>A3m1Vera</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>4.10</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>4.10</t>
+          <t>4.20</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>KEflYcbt</t>
+          <t>8lOY3V6E</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -485,107 +485,107 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>2.45</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>EyfhXHDn</t>
+          <t>ITj9TZCB</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>4.10</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>2.63</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>SvbdWyTh</t>
+          <t>lfn5UFc5</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>2.80</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>AoWGqXpJ</t>
+          <t>dKkDSgSH</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>4.33</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>5.75</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>trWntSE7</t>
+          <t>vquIRDsO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>4.60</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>6.10</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>A3m1Vera</t>
+          <t>jDDw3kMK</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -595,63 +595,63 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>4.10</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>8lOY3V6E</t>
+          <t>xUcLQXdU</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>2.50</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>ITj9TZCB</t>
+          <t>EkZQoHSu</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>3.90</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>3.50</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>lfn5UFc5</t>
+          <t>htYUpyrn</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -661,19 +661,19 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>3.50</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>dKkDSgSH</t>
+          <t>AHSZqech</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -683,185 +683,205 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>3.10</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>vquIRDsO</t>
+          <t>l8RwqFCb</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>4.20</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>2.60</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>jDDw3kMK</t>
+          <t>foKU4Bi8</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>4.50</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>6.00</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>xUcLQXdU</t>
+          <t>rVQsrZR4</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>5.25</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>EkZQoHSu</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2.05</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>3.80</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
-      </c>
+          <t>dYUosgsB</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>htYUpyrn</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2.05</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
+          <t>U3Cs29yR</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>AHSZqech</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>3.75</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>2.80</t>
-        </is>
-      </c>
+          <t>vcKjtDdH</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>l8RwqFCb</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2.60</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>2.50</t>
-        </is>
-      </c>
+          <t>Me49cTqr</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>foKU4Bi8</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>1.44</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>4.60</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>6.50</t>
-        </is>
-      </c>
+          <t>ImJfuXBN</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>0n3Ddmal</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>SM4QZAZp</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>URr9bfCo</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>QDIbviRT</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>rVnDcERi</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr"/>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>xhnHdYtb</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>GroLehd4</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr"/>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>YJuQfCBA</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr"/>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/usa/p6_deployment/data_understanding/df_match_next_odds.xlsx
+++ b/data/usa/p6_deployment/data_understanding/df_match_next_odds.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D28"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,12 +458,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>4.10</t>
+          <t>4.33</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>4.20</t>
+          <t>4.33</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -497,7 +497,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -507,7 +507,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>2.80</t>
         </is>
       </c>
     </row>
@@ -519,7 +519,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -529,7 +529,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>3.00</t>
         </is>
       </c>
     </row>
@@ -541,17 +541,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>5.75</t>
+          <t>7.00</t>
         </is>
       </c>
     </row>
@@ -563,12 +563,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>4.60</t>
+          <t>4.80</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -585,17 +585,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>4.10</t>
+          <t>3.90</t>
         </is>
       </c>
     </row>
@@ -607,17 +607,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>2.55</t>
         </is>
       </c>
     </row>
@@ -629,17 +629,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>3.90</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>4.10</t>
         </is>
       </c>
     </row>
@@ -651,7 +651,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -661,7 +661,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>3.60</t>
         </is>
       </c>
     </row>
@@ -673,17 +673,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>3.60</t>
         </is>
       </c>
     </row>
@@ -695,17 +695,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
           <t>2.45</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>3.70</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>2.60</t>
         </is>
       </c>
     </row>
@@ -722,7 +722,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -739,149 +739,19 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>4.10</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>5.25</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>dYUosgsB</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>U3Cs29yR</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>vcKjtDdH</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>Me49cTqr</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>ImJfuXBN</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>0n3Ddmal</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr"/>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>SM4QZAZp</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr"/>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="inlineStr">
-        <is>
-          <t>URr9bfCo</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr"/>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="inlineStr">
-        <is>
-          <t>QDIbviRT</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr"/>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>rVnDcERi</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr"/>
-      <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="1" t="inlineStr">
-        <is>
-          <t>xhnHdYtb</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr"/>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="1" t="inlineStr">
-        <is>
-          <t>GroLehd4</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr"/>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="1" t="inlineStr">
-        <is>
-          <t>YJuQfCBA</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr"/>
-      <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr"/>
+          <t>6.00</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/usa/p6_deployment/data_understanding/df_match_next_odds.xlsx
+++ b/data/usa/p6_deployment/data_understanding/df_match_next_odds.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,232 +448,232 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>A3m1Vera</t>
+          <t>CAvUgWQG</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>2.55</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>8lOY3V6E</t>
+          <t>6XwYhjtN</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>4.10</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>4.50</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>ITj9TZCB</t>
+          <t>rBhIe7Ef</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>3.00</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>lfn5UFc5</t>
+          <t>I7sxhAeT</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>4.75</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>dKkDSgSH</t>
+          <t>OlK4mU3p</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
           <t>4.75</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>7.00</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>vquIRDsO</t>
+          <t>2uJ8nlJj</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>4.80</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>6.10</t>
+          <t>2.45</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>jDDw3kMK</t>
+          <t>jeCjBXei</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>3.90</t>
+          <t>2.20</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>xUcLQXdU</t>
+          <t>CA0a9BQ3</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>2.38</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>EkZQoHSu</t>
+          <t>UoBfAiBc</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>4.10</t>
+          <t>3.60</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>htYUpyrn</t>
+          <t>tdBLfRT0</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>3.90</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>4.50</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>AHSZqech</t>
+          <t>QD438VuA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -683,73 +683,51 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>3.90</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>l8RwqFCb</t>
+          <t>zJAPgoq7</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>4.00</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>foKU4Bi8</t>
+          <t>Kz477keG</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>6.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>rVQsrZR4</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>1.57</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>4.10</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>6.00</t>
+          <t>2.50</t>
         </is>
       </c>
     </row>

--- a/data/usa/p6_deployment/data_understanding/df_match_next_odds.xlsx
+++ b/data/usa/p6_deployment/data_understanding/df_match_next_odds.xlsx
@@ -448,12 +448,12 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>CAvUgWQG</t>
+          <t>YuZ4CywD</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -463,217 +463,217 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>2.75</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>6XwYhjtN</t>
+          <t>UuWb8pb0</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>4.10</t>
+          <t>4.20</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>4.33</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>rBhIe7Ef</t>
+          <t>llHizuVJ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>4.33</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>4.10</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>I7sxhAeT</t>
+          <t>CWX8BehJ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>3.10</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>OlK4mU3p</t>
+          <t>pK2NUIhs</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>3.90</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>2.63</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>2uJ8nlJj</t>
+          <t>MFWf9Qrf</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>4.10</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>4.10</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>jeCjBXei</t>
+          <t>r5LQTx8m</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>2.25</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>CA0a9BQ3</t>
+          <t>QTAVSdNg</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>2.45</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>UoBfAiBc</t>
+          <t>4K9ZRGx0</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>2.60</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>tdBLfRT0</t>
+          <t>YgEwRzh6</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>3.90</t>
+          <t>5.25</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>5.25</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>QD438VuA</t>
+          <t>CpDsQf7C</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -683,51 +683,51 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>3.90</t>
+          <t>2.15</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>zJAPgoq7</t>
+          <t>SvGeZbpQ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>4.50</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>5.75</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Kz477keG</t>
+          <t>f92nPEMI</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>5.25</t>
         </is>
       </c>
     </row>
